--- a/GBDS JULY FILES 2026/PIRM 2026 Q3.xlsx
+++ b/GBDS JULY FILES 2026/PIRM 2026 Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9531FA75-10B8-48AE-97CC-DB8D69797572}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2470AF5-EA2A-4E7E-9BAF-8F5025C78E77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{90A4BF69-F41C-4D57-82A3-8979CB5194E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{90A4BF69-F41C-4D57-82A3-8979CB5194E7}"/>
   </bookViews>
   <sheets>
     <sheet name="PIRM 2026 Q3" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -105,9 +105,6 @@
     <t>2026 Q3</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>07/28/2026</t>
   </si>
   <si>
@@ -118,6 +115,18 @@
   </si>
   <si>
     <t>PROJECT CROSSBOWS</t>
+  </si>
+  <si>
+    <t>07/29/2026</t>
+  </si>
+  <si>
+    <t>DANYEN STORE</t>
+  </si>
+  <si>
+    <t>POB, SINDANGAN</t>
+  </si>
+  <si>
+    <t>ACKN.</t>
   </si>
 </sst>
 </file>
@@ -930,7 +939,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C4" s="7">
         <f>SUM(C9:C142)</f>
-        <v>5850</v>
+        <v>16250</v>
       </c>
       <c r="D4" s="7">
         <f>SUM(D7:D87)</f>
@@ -938,7 +947,7 @@
       </c>
       <c r="E4" s="8">
         <f>D4-C4</f>
-        <v>101937</v>
+        <v>91537</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -974,7 +983,7 @@
         <v>13</v>
       </c>
       <c r="M5" s="51" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1031,7 +1040,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>21</v>
@@ -1044,7 +1053,7 @@
       <c r="E9" s="19"/>
       <c r="F9" s="22"/>
       <c r="G9" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="19">
         <v>9</v>
@@ -1053,10 +1062,10 @@
         <v>17</v>
       </c>
       <c r="J9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>27</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>19</v>
@@ -1064,19 +1073,38 @@
       <c r="M9" s="50"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="31"/>
+      <c r="A10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="30">
+        <f>650*H10</f>
+        <v>10400</v>
+      </c>
       <c r="D10" s="32"/>
       <c r="E10" s="19"/>
       <c r="F10" s="22"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="G10" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="19">
+        <v>16</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="L10" s="23"/>
-      <c r="M10" s="50"/>
+      <c r="M10" s="50">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
@@ -2980,17 +3008,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="G5:G6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
